--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L946"/>
+  <dimension ref="A1:L950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48831,12 +48831,12 @@
           <t>⤷ 5/25</t>
         </is>
       </c>
-      <c r="G896" t="inlineStr">
-        <is>
-          <t>5:00 pm</t>
-        </is>
-      </c>
-      <c r="H896" t="inlineStr"/>
+      <c r="G896" t="inlineStr"/>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
       <c r="I896" t="inlineStr">
         <is>
           <t>Eugene</t>
@@ -48939,12 +48939,12 @@
           <t>⤷ 5/25</t>
         </is>
       </c>
-      <c r="G898" t="inlineStr">
-        <is>
-          <t>5:00 pm</t>
-        </is>
-      </c>
-      <c r="H898" t="inlineStr"/>
+      <c r="G898" t="inlineStr"/>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>1 - 16</t>
+        </is>
+      </c>
       <c r="I898" t="inlineStr">
         <is>
           <t>St. Paul Lutheran (Concordia)</t>
@@ -49047,12 +49047,12 @@
           <t>⤷ 5/26</t>
         </is>
       </c>
-      <c r="G900" t="inlineStr">
-        <is>
-          <t>5:00 pm</t>
-        </is>
-      </c>
-      <c r="H900" t="inlineStr"/>
+      <c r="G900" t="inlineStr"/>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>4 - 1</t>
+        </is>
+      </c>
       <c r="I900" t="inlineStr">
         <is>
           <t>Holden</t>
@@ -49155,12 +49155,12 @@
           <t>⤷ 5/26</t>
         </is>
       </c>
-      <c r="G902" t="inlineStr">
-        <is>
-          <t>5:00 pm</t>
-        </is>
-      </c>
-      <c r="H902" t="inlineStr"/>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
       <c r="I902" t="inlineStr">
         <is>
           <t>Fatima</t>
@@ -49263,12 +49263,12 @@
           <t>⤷ 5/26</t>
         </is>
       </c>
-      <c r="G904" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H904" t="inlineStr"/>
+      <c r="G904" t="inlineStr"/>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>3 - 12</t>
+        </is>
+      </c>
       <c r="I904" t="inlineStr">
         <is>
           <t>Springfield Catholic</t>
@@ -49371,12 +49371,12 @@
           <t>⤷ 5/26</t>
         </is>
       </c>
-      <c r="G906" t="inlineStr">
-        <is>
-          <t>6:00 pm</t>
-        </is>
-      </c>
-      <c r="H906" t="inlineStr"/>
+      <c r="G906" t="inlineStr"/>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>4 - 1</t>
+        </is>
+      </c>
       <c r="I906" t="inlineStr">
         <is>
           <t>Moberly</t>
@@ -49479,12 +49479,12 @@
           <t>⤷ 5/26</t>
         </is>
       </c>
-      <c r="G908" t="inlineStr">
-        <is>
-          <t>6:00 pm</t>
-        </is>
-      </c>
-      <c r="H908" t="inlineStr"/>
+      <c r="G908" t="inlineStr"/>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>1 - 4</t>
+        </is>
+      </c>
       <c r="I908" t="inlineStr">
         <is>
           <t>Mexico</t>
@@ -49508,21 +49508,21 @@
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>953</v>
+        <v>217</v>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Battle High School</t>
+          <t>Blair Oaks High School</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Track and Field Boys</t>
+          <t>Baseball Spring Season</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -49532,14 +49532,18 @@
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>5/29-30</t>
+          <t>⤷ 5/28</t>
         </is>
       </c>
       <c r="G909" t="inlineStr"/>
-      <c r="H909" t="inlineStr"/>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>12 - 0</t>
+        </is>
+      </c>
       <c r="I909" t="inlineStr">
         <is>
-          <t>Class 5 State Tournament</t>
+          <t>Carrollton</t>
         </is>
       </c>
       <c r="J909" t="inlineStr">
@@ -49549,32 +49553,32 @@
       </c>
       <c r="K909" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=953&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=217&amp;alg=3</t>
         </is>
       </c>
       <c r="L909" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=5&amp;year=2025</t>
+          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=217&amp;alg=3&amp;comp=2727514</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>953</v>
+        <v>128</v>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>Battle High School</t>
+          <t>Mexico High School</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Track and Field Girls</t>
+          <t>Baseball Spring Season</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -49584,14 +49588,18 @@
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>5/29-30</t>
+          <t>⤷ 5/28</t>
         </is>
       </c>
       <c r="G910" t="inlineStr"/>
-      <c r="H910" t="inlineStr"/>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>3 - 13</t>
+        </is>
+      </c>
       <c r="I910" t="inlineStr">
         <is>
-          <t>Class 5 State Tournament</t>
+          <t>Orchard Farm</t>
         </is>
       </c>
       <c r="J910" t="inlineStr">
@@ -49601,22 +49609,22 @@
       </c>
       <c r="K910" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=953&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=128&amp;alg=3</t>
         </is>
       </c>
       <c r="L910" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=5&amp;year=2025</t>
+          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=128&amp;alg=3&amp;comp=2727536</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>26</v>
+        <v>953</v>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Camdenton High School</t>
+          <t>Battle High School</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -49643,7 +49651,7 @@
       <c r="H911" t="inlineStr"/>
       <c r="I911" t="inlineStr">
         <is>
-          <t>Class 4 State Tournament</t>
+          <t>Class 5 State Tournament</t>
         </is>
       </c>
       <c r="J911" t="inlineStr">
@@ -49653,22 +49661,22 @@
       </c>
       <c r="K911" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=26&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=953&amp;alg=52</t>
         </is>
       </c>
       <c r="L911" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=5&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="n">
-        <v>26</v>
+        <v>953</v>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Camdenton High School</t>
+          <t>Battle High School</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -49695,7 +49703,7 @@
       <c r="H912" t="inlineStr"/>
       <c r="I912" t="inlineStr">
         <is>
-          <t>Class 4 State Tournament</t>
+          <t>Class 5 State Tournament</t>
         </is>
       </c>
       <c r="J912" t="inlineStr">
@@ -49705,22 +49713,22 @@
       </c>
       <c r="K912" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=26&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=953&amp;alg=53</t>
         </is>
       </c>
       <c r="L912" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=5&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>1540</v>
+        <v>26</v>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Capital City High School</t>
+          <t>Camdenton High School</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -49757,7 +49765,7 @@
       </c>
       <c r="K913" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=26&amp;alg=52</t>
         </is>
       </c>
       <c r="L913" t="inlineStr">
@@ -49768,11 +49776,11 @@
     </row>
     <row r="914">
       <c r="A914" t="n">
-        <v>1540</v>
+        <v>26</v>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>Capital City High School</t>
+          <t>Camdenton High School</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -49809,7 +49817,7 @@
       </c>
       <c r="K914" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=26&amp;alg=53</t>
         </is>
       </c>
       <c r="L914" t="inlineStr">
@@ -49820,11 +49828,11 @@
     </row>
     <row r="915">
       <c r="A915" t="n">
-        <v>917</v>
+        <v>1540</v>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Father Tolton</t>
+          <t>Capital City High School</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -49861,7 +49869,7 @@
       </c>
       <c r="K915" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=917&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=52</t>
         </is>
       </c>
       <c r="L915" t="inlineStr">
@@ -49872,11 +49880,11 @@
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>917</v>
+        <v>1540</v>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>Father Tolton</t>
+          <t>Capital City High School</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -49903,7 +49911,7 @@
       <c r="H916" t="inlineStr"/>
       <c r="I916" t="inlineStr">
         <is>
-          <t>MSHSAA Class 4 State Championships</t>
+          <t>Class 4 State Tournament</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
@@ -49913,12 +49921,12 @@
       </c>
       <c r="K916" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=917&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=53</t>
         </is>
       </c>
       <c r="L916" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Tournament.aspx?s=917&amp;alg=53&amp;tournament=563970</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
@@ -49933,12 +49941,12 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Track and Field Girls</t>
+          <t>Track and Field Boys</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -49965,32 +49973,32 @@
       </c>
       <c r="K917" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=917&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=917&amp;alg=52</t>
         </is>
       </c>
       <c r="L917" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>80</v>
+        <v>917</v>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Fulton High School</t>
+          <t>Father Tolton</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Track and Field Boys</t>
+          <t>Track and Field Girls</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -50007,7 +50015,7 @@
       <c r="H918" t="inlineStr"/>
       <c r="I918" t="inlineStr">
         <is>
-          <t>Class 4 State Tournament</t>
+          <t>MSHSAA Class 4 State Championships</t>
         </is>
       </c>
       <c r="J918" t="inlineStr">
@@ -50017,22 +50025,22 @@
       </c>
       <c r="K918" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=80&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=917&amp;alg=53</t>
         </is>
       </c>
       <c r="L918" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/MySchool/Tournament.aspx?s=917&amp;alg=53&amp;tournament=563970</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>80</v>
+        <v>917</v>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Fulton High School</t>
+          <t>Father Tolton</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -50069,7 +50077,7 @@
       </c>
       <c r="K919" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=80&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=917&amp;alg=53</t>
         </is>
       </c>
       <c r="L919" t="inlineStr">
@@ -50080,11 +50088,11 @@
     </row>
     <row r="920">
       <c r="A920" t="n">
-        <v>522</v>
+        <v>80</v>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>Helias High School</t>
+          <t>Fulton High School</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -50111,7 +50119,7 @@
       <c r="H920" t="inlineStr"/>
       <c r="I920" t="inlineStr">
         <is>
-          <t>Class 5 State Tournament</t>
+          <t>Class 4 State Tournament</t>
         </is>
       </c>
       <c r="J920" t="inlineStr">
@@ -50121,22 +50129,22 @@
       </c>
       <c r="K920" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=80&amp;alg=52</t>
         </is>
       </c>
       <c r="L920" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=5&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="n">
-        <v>522</v>
+        <v>80</v>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Helias High School</t>
+          <t>Fulton High School</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -50163,7 +50171,7 @@
       <c r="H921" t="inlineStr"/>
       <c r="I921" t="inlineStr">
         <is>
-          <t>Class 5 State Tournament</t>
+          <t>Class 4 State Tournament</t>
         </is>
       </c>
       <c r="J921" t="inlineStr">
@@ -50173,22 +50181,22 @@
       </c>
       <c r="K921" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=80&amp;alg=53</t>
         </is>
       </c>
       <c r="L921" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=5&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>85</v>
+        <v>522</v>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Hickman High School</t>
+          <t>Helias High School</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -50225,7 +50233,7 @@
       </c>
       <c r="K922" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=85&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=52</t>
         </is>
       </c>
       <c r="L922" t="inlineStr">
@@ -50236,11 +50244,11 @@
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>85</v>
+        <v>522</v>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Hickman High School</t>
+          <t>Helias High School</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -50277,7 +50285,7 @@
       </c>
       <c r="K923" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=85&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=53</t>
         </is>
       </c>
       <c r="L923" t="inlineStr">
@@ -50288,11 +50296,11 @@
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>Jefferson City High School</t>
+          <t>Hickman High School</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -50319,7 +50327,7 @@
       <c r="H924" t="inlineStr"/>
       <c r="I924" t="inlineStr">
         <is>
-          <t>Class 4 State Tournament</t>
+          <t>Class 5 State Tournament</t>
         </is>
       </c>
       <c r="J924" t="inlineStr">
@@ -50329,22 +50337,22 @@
       </c>
       <c r="K924" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=84&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=85&amp;alg=52</t>
         </is>
       </c>
       <c r="L924" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=5&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Jefferson City High School</t>
+          <t>Hickman High School</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -50371,7 +50379,7 @@
       <c r="H925" t="inlineStr"/>
       <c r="I925" t="inlineStr">
         <is>
-          <t>Class 4 State Tournament</t>
+          <t>Class 5 State Tournament</t>
         </is>
       </c>
       <c r="J925" t="inlineStr">
@@ -50381,22 +50389,22 @@
       </c>
       <c r="K925" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=84&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=85&amp;alg=53</t>
         </is>
       </c>
       <c r="L925" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=5&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>Marshall High School</t>
+          <t>Jefferson City High School</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -50433,7 +50441,7 @@
       </c>
       <c r="K926" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=360&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=84&amp;alg=52</t>
         </is>
       </c>
       <c r="L926" t="inlineStr">
@@ -50444,11 +50452,11 @@
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Marshall High School</t>
+          <t>Jefferson City High School</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -50485,7 +50493,7 @@
       </c>
       <c r="K927" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=360&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=84&amp;alg=53</t>
         </is>
       </c>
       <c r="L927" t="inlineStr">
@@ -50496,11 +50504,11 @@
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>Mexico High School</t>
+          <t>Marshall High School</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -50537,7 +50545,7 @@
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=128&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=360&amp;alg=52</t>
         </is>
       </c>
       <c r="L928" t="inlineStr">
@@ -50548,11 +50556,11 @@
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Mexico High School</t>
+          <t>Marshall High School</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -50589,7 +50597,7 @@
       </c>
       <c r="K929" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=128&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=360&amp;alg=53</t>
         </is>
       </c>
       <c r="L929" t="inlineStr">
@@ -50600,11 +50608,11 @@
     </row>
     <row r="930">
       <c r="A930" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>Moberly High School</t>
+          <t>Mexico High School</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -50641,7 +50649,7 @@
       </c>
       <c r="K930" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=132&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=128&amp;alg=52</t>
         </is>
       </c>
       <c r="L930" t="inlineStr">
@@ -50652,11 +50660,11 @@
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Moberly High School</t>
+          <t>Mexico High School</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -50693,7 +50701,7 @@
       </c>
       <c r="K931" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=132&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=128&amp;alg=53</t>
         </is>
       </c>
       <c r="L931" t="inlineStr">
@@ -50704,11 +50712,11 @@
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>Osage High School</t>
+          <t>Moberly High School</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -50745,7 +50753,7 @@
       </c>
       <c r="K932" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=152&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=132&amp;alg=52</t>
         </is>
       </c>
       <c r="L932" t="inlineStr">
@@ -50756,11 +50764,11 @@
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Osage High School</t>
+          <t>Moberly High School</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -50797,7 +50805,7 @@
       </c>
       <c r="K933" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=152&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=132&amp;alg=53</t>
         </is>
       </c>
       <c r="L933" t="inlineStr">
@@ -50808,11 +50816,11 @@
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>578</v>
+        <v>152</v>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Rock Bridge High School</t>
+          <t>Osage High School</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -50839,7 +50847,7 @@
       <c r="H934" t="inlineStr"/>
       <c r="I934" t="inlineStr">
         <is>
-          <t>Class 5 State Tournament</t>
+          <t>Class 4 State Tournament</t>
         </is>
       </c>
       <c r="J934" t="inlineStr">
@@ -50849,22 +50857,22 @@
       </c>
       <c r="K934" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=152&amp;alg=52</t>
         </is>
       </c>
       <c r="L934" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=5&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>578</v>
+        <v>152</v>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Rock Bridge High School</t>
+          <t>Osage High School</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -50891,7 +50899,7 @@
       <c r="H935" t="inlineStr"/>
       <c r="I935" t="inlineStr">
         <is>
-          <t>Class 5 State Tournament</t>
+          <t>Class 4 State Tournament</t>
         </is>
       </c>
       <c r="J935" t="inlineStr">
@@ -50901,22 +50909,22 @@
       </c>
       <c r="K935" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=152&amp;alg=53</t>
         </is>
       </c>
       <c r="L935" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=5&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="n">
-        <v>194</v>
+        <v>578</v>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Smith-Cotton High School</t>
+          <t>Rock Bridge High School</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -50953,7 +50961,7 @@
       </c>
       <c r="K936" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=194&amp;alg=52</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=52</t>
         </is>
       </c>
       <c r="L936" t="inlineStr">
@@ -50964,11 +50972,11 @@
     </row>
     <row r="937">
       <c r="A937" t="n">
-        <v>194</v>
+        <v>578</v>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Smith-Cotton High School</t>
+          <t>Rock Bridge High School</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -51005,7 +51013,7 @@
       </c>
       <c r="K937" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=194&amp;alg=53</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=53</t>
         </is>
       </c>
       <c r="L937" t="inlineStr">
@@ -51016,21 +51024,21 @@
     </row>
     <row r="938">
       <c r="A938" t="n">
-        <v>953</v>
+        <v>194</v>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>Battle High School</t>
+          <t>Smith-Cotton High School</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Soccer Girls</t>
+          <t>Track and Field Boys</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -51040,14 +51048,14 @@
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t>5/30-6/6</t>
+          <t>5/29-30</t>
         </is>
       </c>
       <c r="G938" t="inlineStr"/>
       <c r="H938" t="inlineStr"/>
       <c r="I938" t="inlineStr">
         <is>
-          <t>Class 4 State Tournament</t>
+          <t>Class 5 State Tournament</t>
         </is>
       </c>
       <c r="J938" t="inlineStr">
@@ -51057,32 +51065,32 @@
       </c>
       <c r="K938" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=953&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=194&amp;alg=52</t>
         </is>
       </c>
       <c r="L938" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=52&amp;class=5&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>1540</v>
+        <v>194</v>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Capital City High School</t>
+          <t>Smith-Cotton High School</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Soccer Girls</t>
+          <t>Track and Field Girls</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -51092,14 +51100,14 @@
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t>5/30-6/6</t>
+          <t>5/29-30</t>
         </is>
       </c>
       <c r="G939" t="inlineStr"/>
       <c r="H939" t="inlineStr"/>
       <c r="I939" t="inlineStr">
         <is>
-          <t>Class 3 State Tournament</t>
+          <t>Class 5 State Tournament</t>
         </is>
       </c>
       <c r="J939" t="inlineStr">
@@ -51109,22 +51117,22 @@
       </c>
       <c r="K939" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=194&amp;alg=53</t>
         </is>
       </c>
       <c r="L939" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=3&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/PostseasonResult.aspx?alg=53&amp;class=5&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>1540</v>
+        <v>953</v>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>Capital City High School</t>
+          <t>Battle High School</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
@@ -51144,18 +51152,14 @@
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t>⤷ 5/30</t>
-        </is>
-      </c>
-      <c r="G940" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
+          <t>5/30-6/6</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr"/>
       <c r="H940" t="inlineStr"/>
       <c r="I940" t="inlineStr">
         <is>
-          <t>Carl Junction</t>
+          <t>Class 4 State Tournament</t>
         </is>
       </c>
       <c r="J940" t="inlineStr">
@@ -51165,22 +51169,22 @@
       </c>
       <c r="K940" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=953&amp;alg=34</t>
         </is>
       </c>
       <c r="L940" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=1540&amp;alg=34&amp;comp=2727596</t>
+          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>522</v>
+        <v>1540</v>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Helias High School</t>
+          <t>Capital City High School</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -51217,7 +51221,7 @@
       </c>
       <c r="K941" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=34</t>
         </is>
       </c>
       <c r="L941" t="inlineStr">
@@ -51228,11 +51232,11 @@
     </row>
     <row r="942">
       <c r="A942" t="n">
-        <v>522</v>
+        <v>1540</v>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>Helias High School</t>
+          <t>Capital City High School</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -51255,15 +51259,15 @@
           <t>⤷ 5/30</t>
         </is>
       </c>
-      <c r="G942" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H942" t="inlineStr"/>
+      <c r="G942" t="inlineStr"/>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>4 - 1</t>
+        </is>
+      </c>
       <c r="I942" t="inlineStr">
         <is>
-          <t>Ft. Zumwalt South</t>
+          <t>Carl Junction</t>
         </is>
       </c>
       <c r="J942" t="inlineStr">
@@ -51273,22 +51277,22 @@
       </c>
       <c r="K942" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=34</t>
         </is>
       </c>
       <c r="L942" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=522&amp;alg=34&amp;comp=2727597</t>
+          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=1540&amp;alg=34&amp;comp=2727596</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>578</v>
+        <v>522</v>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Rock Bridge High School</t>
+          <t>Helias High School</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -51315,7 +51319,7 @@
       <c r="H943" t="inlineStr"/>
       <c r="I943" t="inlineStr">
         <is>
-          <t>Class 4 State Tournament</t>
+          <t>Class 3 State Tournament</t>
         </is>
       </c>
       <c r="J943" t="inlineStr">
@@ -51325,22 +51329,22 @@
       </c>
       <c r="K943" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=34</t>
         </is>
       </c>
       <c r="L943" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=4&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=3&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>578</v>
+        <v>522</v>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Rock Bridge High School</t>
+          <t>Helias High School</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -51363,15 +51367,15 @@
           <t>⤷ 5/30</t>
         </is>
       </c>
-      <c r="G944" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H944" t="inlineStr"/>
+      <c r="G944" t="inlineStr"/>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>0 - 2</t>
+        </is>
+      </c>
       <c r="I944" t="inlineStr">
         <is>
-          <t>Rock Bridge</t>
+          <t>Ft. Zumwalt South</t>
         </is>
       </c>
       <c r="J944" t="inlineStr">
@@ -51381,22 +51385,22 @@
       </c>
       <c r="K944" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=522&amp;alg=34</t>
         </is>
       </c>
       <c r="L944" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=578&amp;alg=34&amp;comp=2727606</t>
+          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=522&amp;alg=34&amp;comp=2727597</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>2</v>
+        <v>578</v>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Southern Boone High School</t>
+          <t>Rock Bridge High School</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -51423,7 +51427,7 @@
       <c r="H945" t="inlineStr"/>
       <c r="I945" t="inlineStr">
         <is>
-          <t>Class 2 State Tournament</t>
+          <t>Class 4 State Tournament</t>
         </is>
       </c>
       <c r="J945" t="inlineStr">
@@ -51433,68 +51437,288 @@
       </c>
       <c r="K945" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=2&amp;alg=34</t>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=34</t>
         </is>
       </c>
       <c r="L945" t="inlineStr">
         <is>
-          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=2&amp;year=2025</t>
+          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=4&amp;year=2025</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
+        <v>578</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Rock Bridge High School</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Soccer Girls</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Varsity</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>⤷ 5/30</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr"/>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>0 - 1</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>Nixa</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>tournament</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=578&amp;alg=34</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=578&amp;alg=34&amp;comp=2727606</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
         <v>2</v>
       </c>
-      <c r="B946" t="inlineStr">
+      <c r="B947" t="inlineStr">
         <is>
           <t>Southern Boone High School</t>
         </is>
       </c>
-      <c r="C946" t="inlineStr">
+      <c r="C947" t="inlineStr">
         <is>
           <t>Soccer Girls</t>
         </is>
       </c>
-      <c r="D946" t="inlineStr">
+      <c r="D947" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E946" t="inlineStr">
-        <is>
-          <t>Varsity</t>
-        </is>
-      </c>
-      <c r="F946" t="inlineStr">
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Varsity</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>5/30-6/6</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr"/>
+      <c r="H947" t="inlineStr"/>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Class 2 State Tournament</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>tournament</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=2&amp;alg=34</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/Activities/DistrictWinners.aspx?alg=34&amp;class=2&amp;year=2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>2</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Southern Boone High School</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Soccer Girls</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Varsity</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
         <is>
           <t>⤷ 5/30</t>
         </is>
       </c>
-      <c r="G946" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H946" t="inlineStr"/>
-      <c r="I946" t="inlineStr">
+      <c r="G948" t="inlineStr"/>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>0 - 3</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
         <is>
           <t>Springfield Catholic</t>
         </is>
       </c>
-      <c r="J946" t="inlineStr">
-        <is>
-          <t>tournament</t>
-        </is>
-      </c>
-      <c r="K946" t="inlineStr">
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>tournament</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
         <is>
           <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=2&amp;alg=34</t>
         </is>
       </c>
-      <c r="L946" t="inlineStr">
+      <c r="L948" t="inlineStr">
         <is>
           <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=2&amp;alg=34&amp;comp=2727586</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>217</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Blair Oaks High School</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Baseball Spring Season</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Varsity</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>⤷ 6/3</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>7:00 pm</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr"/>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>Licking</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>tournament</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=217&amp;alg=3</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=217&amp;alg=3&amp;comp=2727518</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Capital City High School</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Soccer Girls</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Varsity</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>⤷ 6/5</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>1:30 pm</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr"/>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>St. Michael the Archangel</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>tournament</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/MySchool/Schedule.aspx?s=1540&amp;alg=34</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>https://www.mshsaa.org/MySchool/Matchup.aspx?s=1540&amp;alg=34&amp;comp=2727599</t>
         </is>
       </c>
     </row>
